--- a/planogram-sprint-plan.xlsx
+++ b/planogram-sprint-plan.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Sprint Plan" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Design Spec" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,9 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="167">
-  <si>
-    <t xml:space="preserve">Sprint 1 Date (9/28 - 10/9)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="160">
+  <si>
+    <t xml:space="preserve">Sprint 1 Date (9/28 - 10/9) - 2 weeks</t>
   </si>
   <si>
     <t xml:space="preserve">Efforts (In Days)</t>
@@ -68,7 +69,7 @@
     <t xml:space="preserve">To Do</t>
   </si>
   <si>
-    <t xml:space="preserve">Monthly folder library (CPG, MPG, Common), Status and RunId columns, Power Automate 'For a selected file' Ready button, manifest check of required files, HTTPS call to ADF createRun</t>
+    <t xml:space="preserve">Monthly folder library (CPG, MPG, Common), Status and RunId columns, Power Automate 'For a selected file' Ready button, manifest check, HTTPS call to ADF createRun</t>
   </si>
   <si>
     <t xml:space="preserve">ADF Configuration</t>
@@ -86,13 +87,19 @@
     <t xml:space="preserve">Total effort (person-days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 2 Date (10/12 - 10/23)</t>
+    <t xml:space="preserve">Weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2 Date (10/12 - 10/23) - 2 weeks</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint Goal: CPG core: files and Snowflake data land in staging and rules Q1-Q19 run in order, producing candidate CPG results on realistic 60-70k-row files.</t>
   </si>
   <si>
-    <t xml:space="preserve">Overview of tasks: Build ingestion at volume, implement all 19 CPG rules, and chain them through ADF.</t>
+    <t xml:space="preserve">Overview of tasks: Build ingestion at volume, implement all 19 CPG rules, chain them through ADF.</t>
   </si>
   <si>
     <t xml:space="preserve">Snowflake reference data copy</t>
@@ -116,9 +123,6 @@
     <t xml:space="preserve">Set-based stored procedures: item link, monthly changes, discontinued items, new items</t>
   </si>
   <si>
-    <t xml:space="preserve">Excel to staging bulk load</t>
-  </si>
-  <si>
     <t xml:space="preserve">CPG business rules Q11-Q19</t>
   </si>
   <si>
@@ -137,13 +141,13 @@
     <t xml:space="preserve">cpg.* tables for Planogram Master, Monthly New Item and DN27 candidates</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 3 Date (10/26 - 11/6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint Goal: CPG complete: validation, human approval, the 3 CPG files and the handoff to the external team work end to end and are ready for business UAT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overview of tasks: Validation SPs and exception queue, Power Apps review, approval gate, file generation, handoff notification, full CPG test at volume.</t>
+    <t xml:space="preserve">Sprint 3 Date (10/26 - 11/13) - 3 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint Goal: CPG complete and MPG intake ready: validation, human approval, the 3 CPG files and the handoff work end to end; MPG trigger and Excel ingest are built; RPA bot started on a sample file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview of tasks: Validation SPs and exception queue, Power Apps review, approval gate, file generation, handoff, full CPG test at volume, Ready for MPG button, MPG Excel ingest, RPA bot build on sample XREF.</t>
   </si>
   <si>
     <t xml:space="preserve">CPG validation SPs + exception table</t>
@@ -158,9 +162,6 @@
     <t xml:space="preserve">Canvas app over SQL views, server-side filter and paging, fix or resolve with reason, revalidate trigger</t>
   </si>
   <si>
-    <t xml:space="preserve">CPG validation SPs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Approval gate (Teams card + ADF Webhook)</t>
   </si>
   <si>
@@ -173,34 +174,22 @@
     <t xml:space="preserve">ADF Copy from SQL to Planogram Master Data, Monthly New Item, DN27 with checksum into outputs/CPG</t>
   </si>
   <si>
-    <t xml:space="preserve">Approval gate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Handoff notification</t>
   </si>
   <si>
     <t xml:space="preserve">Secure SharePoint Outbound/RUN_ID link (no attachments), Teams or email message, AWAITING_TEAM status, SLA reminder flow</t>
   </si>
   <si>
-    <t xml:space="preserve">CPG end-to-end test at volume + UAT fixes</t>
+    <t xml:space="preserve">CPG end-to-end test at volume + fixes</t>
   </si>
   <si>
     <t xml:space="preserve">Run with 60-70k-row files, measure runtime per step, fix defects</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 4 Date (11/9 - 11/20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint Goal: MPG ingest: the second upload triggers MPG, Excel and PDF inputs are processed, and the first half of the MPG rules run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overview of tasks: Ready for MPG button with dependency guard, Excel and PDF ingestion, Document Intelligence and Azure Function, MPG rules Q1-Q17.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ready for MPG button + dependency guard</t>
   </si>
   <si>
-    <t xml:space="preserve">Second Power Automate button, checks RUN_ID exists and CPG is approved, manifest check (Product_Listings, SOG_PDFs, Category_Adjustments), calls ADF MPG pipeline</t>
+    <t xml:space="preserve">Second Power Automate button, checks RUN_ID exists and CPG approved, manifest check (Product_Listings, SOG_PDFs, Category_Adjustments), calls ADF MPG pipeline</t>
   </si>
   <si>
     <t xml:space="preserve">MPG Excel/CSV ingest + staging</t>
@@ -209,7 +198,19 @@
     <t xml:space="preserve">Copy MPG files into the frozen RUN_ID package and stg.mpg_* with reconciliation</t>
   </si>
   <si>
-    <t xml:space="preserve">Ready for MPG button</t>
+    <t xml:space="preserve">RPA bot build on sample XREF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Automate Desktop unattended bot, cloud flow queue, Key Vault credentials, retries, screenshots on failure; built against a sample file until XREF is ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 4 Date (11/16 - 11/27) - 2 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint Goal: MPG processing complete: PDFs are extracted, all 33 MPG rules run, and MPG validation produces exceptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview of tasks: Document Intelligence and Azure Function for PDFs, MPG rules Q1-Q33, MPG validation SPs.</t>
   </si>
   <si>
     <t xml:space="preserve">PDF extraction with Document Intelligence</t>
@@ -224,201 +225,168 @@
     <t xml:space="preserve">Durable Function (Flex Consumption), normalises output, low confidence goes to exceptions</t>
   </si>
   <si>
+    <t xml:space="preserve">MPG business rules Q1-Q17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly sets, category processing, largest set and related rules as set-based SPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPG business rules Q18-Q33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planogram processing, label construction, item count calculations, validation and export generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPG validation SPs + exceptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid item status, SOG data, description, POG mismatches, item counts; reuse Power Apps review pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 5 Date (11/30 - 12/11) - 2 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint Goal: Go-live ready: MPG approval, SAP XREF and RPA upload work end to end, tested at 3x volume, hardened and signed off in UAT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview of tasks: MPG approval, XREF generation, RPA integration with SAP reconciliation, performance and security hardening, CI/CD to Prod, business UAT and handover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPG approval gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuse Teams card and ADF Webhook pattern, approval_audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP XREF file generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single schema-validated XREF file, row count and hash recorded, saved to outputs/MPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA integration + SAP reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point bot at real XREF, reconcile SAP record count to XREF, failure alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run close + runbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETED status, stakeholder notification, archive package; operations runbook and restart procedures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance test at 3x volume + tuning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200k rows per file, index tuning, SQL scale-up window, copy parallelism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security and monitoring hardening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private endpoints, managed VNet integration runtime, RBAC review, alerts on failure, long run and approval pending, run dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD and Prod deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADF Git CI/CD, DACPAC, Bicep for Prod, tSQLt tests per rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business UAT + defect fixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full CPG to SAP cycle with business users, fix defects, sign-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions: Sprint 1 dates inferred as 9/28-10/9 (two weeks before Sprint 2). Efforts are person-days; Plan runs 11 weeks (about 2.5 months) from 9/28 to 12/11 with sprints of 2, 2, 3, 2, 2 weeks, assuming 2 developers (see Assumptions tab). Load % in the last column of each total row = planned effort / capacity. Leave, holidays and hypercare after 12/11 are not included. Owners are blank for you to assign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Automate 'For a selected file' button on the month folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks manifest of required files, sets Status=Submitted, calls ADF createRun over HTTPS with Entra app or managed identity. Fallback: _READY.flag file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUN_ID = RUN_YYYYMM_nnn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated by ADF, carried in every table, log, folder and notification. One active run per month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landing zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADLS Gen2 raw/YYYY/MM/RUN_ID/{CPG,MPG,PDFs,Reference}, outputs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immutable (WORM) once frozen; lifecycle tiering to cool storage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel ingest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADF Copy to Azure SQL staging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60-70k rows per file; batch 100k; parallel copies; row-count and checksum reconciliation; convert to CSV/Parquet if Excel parsing is slow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure SQL Database (vCore, General Purpose)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale up before the run and down after via ADF Web activity; clustered columnstore on large staging tables; indexes on item, POG, SOG keys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stored procedures: Q1-Q19 (CPG), Q1-Q33 (MPG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set-based only, @RunId parameter, idempotent (delete by RunId then insert), log rows in/out and duration to ctl.processing_step.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orchestration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADF ForEach over ctl.processing_step ordered by sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retries 2 with backoff, fromStep parameter to restart, failure sets status FAILED and alerts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used only for PDF normalisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durable Function on Flex Consumption. Cold start is irrelevant for a monthly batch; keep async to avoid ADF's HTTP timeout.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PDF extraction</t>
   </si>
   <si>
-    <t xml:space="preserve">MPG business rules Q1-Q17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly sets, category processing, largest set and related rules as set-based SPs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPG Excel/CSV ingest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 5 Date (11/23 - 12/4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint Goal: MPG complete and SAP: remaining rules, validation, approval, XREF generation and RPA upload to SAP work end to end.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overview of tasks: MPG rules Q18-Q33, MPG validation and approval, SAP XREF file, RPA bot and run close.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPG business rules Q18-Q33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planogram processing, label construction, item count calculations, validation and export generation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPG validation + exception review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invalid item status, SOG data, description, POG mismatches, item counts; reuse Power Apps pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPG approval gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuse Teams card and ADF Webhook pattern, approval_audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP XREF file generation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single schema-validated XREF file, row count and hash recorded, saved to outputs/MPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA upload bot for SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Automate Desktop unattended bot, cloud flow queues job, credentials from Key Vault, retries, screenshots on failure, SAP record-count reconciliation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run close + notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPLETED status, stakeholder notification, archive package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 6 Date (12/7 - 12/18) - recommended buffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint Goal: Production readiness: tested at volume, secured, monitored, UAT signed off and live. Needed because Sprints 1-5 are already full.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overview of tasks: Performance and security hardening, monitoring, CI/CD, business UAT, runbook and cutover.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance test at 3x volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200k+ rows per file, tune indexes, SQL scale-up window, copy parallelism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPG complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security hardening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private endpoints, managed VNet integration runtime, RBAC review, secrets only in Key Vault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, alerts and run dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log Analytics queries, alerts on failure, long run and approval pending, status dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD to UAT and Prod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADF Git CI/CD, DACPAC deployment, Bicep for infra, tSQLt tests per rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business UAT and defect fixes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full CPG to SAP cycle with business users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runbook, handover and training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations runbook, restart procedures, user guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production cutover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prod deployment, first-month hypercare plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions: Sprint 1 dates inferred as 9/28-10/9 (two weeks before Sprint 2). Efforts are person-days; Sprints 1-5 total about 100, which fits a team of roughly 2 developers. Owners are left blank for you to assign. Sprint 6 is a recommended buffer added beyond your Sprint 5 end date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exact detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Automate 'For a selected file' button on the month folder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checks manifest of required files, sets Status=Submitted, calls ADF createRun over HTTPS with Entra app or managed identity. Fallback: _READY.flag file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUN_ID = RUN_YYYYMM_nnn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by ADF, carried in every table, log, folder and notification. One active run per month.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landing zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADLS Gen2 raw/YYYY/MM/RUN_ID/{CPG,MPG,PDFs,Reference}, outputs/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immutable (WORM) once frozen; lifecycle tiering to cool storage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel ingest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADF Copy to Azure SQL staging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60-70k rows per file; batch 100k; parallel copies; row-count and checksum reconciliation; convert to CSV/Parquet if Excel parsing is slow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure SQL Database (vCore, General Purpose)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale up before the run and down after via ADF Web activity; clustered columnstore on large staging tables; indexes on item, POG, SOG keys.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stored procedures: Q1-Q19 (CPG), Q1-Q33 (MPG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set-based only, @RunId parameter, idempotent (delete by RunId then insert), log rows in/out and duration to ctl.processing_step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orchestration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADF ForEach over ctl.processing_step ordered by sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retries 2 with backoff, fromStep parameter to restart, failure sets status FAILED and alerts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure Functions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Used only for PDF normalisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durable Function on Flex Consumption. Cold start is irrelevant for a monthly batch; keep async to avoid ADF's HTTP timeout.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure AI Document Intelligence</t>
   </si>
   <si>
@@ -522,16 +490,29 @@
   </si>
   <si>
     <t xml:space="preserve">Thresholds, approvers, email lists, rule toggles; no hardcoding in pipelines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit to match the team; capacity on Sprint Plan recalculates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working days per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No holidays or leave deducted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,6 +551,21 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -656,7 +652,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -677,16 +673,32 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -941,7 +953,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -1088,15 +1100,27 @@
         <f aca="false">SUM(B4:B7)</f>
         <v>16</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <f aca="false">Assumptions!$B$1*Assumptions!$B$2*D8</f>
+        <v>20</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <f aca="false">B8/F8</f>
+        <v>0.8</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
@@ -1119,7 +1143,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1130,7 +1154,7 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1141,7 +1165,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>2</v>
@@ -1151,10 +1175,10 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>16</v>
@@ -1162,7 +1186,7 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>3</v>
@@ -1175,7 +1199,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>18</v>
@@ -1183,7 +1207,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>5</v>
@@ -1196,15 +1220,15 @@
         <v>11</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>5</v>
@@ -1217,15 +1241,15 @@
         <v>11</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>3</v>
@@ -1238,15 +1262,15 @@
         <v>11</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>2</v>
@@ -1256,13 +1280,13 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1273,15 +1297,27 @@
         <f aca="false">SUM(B13:B18)</f>
         <v>20</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <f aca="false">Assumptions!$B$1*Assumptions!$B$2*D19</f>
+        <v>20</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <f aca="false">B19/F19</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -1304,7 +1340,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1315,7 +1351,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1326,7 +1362,7 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>4</v>
@@ -1339,15 +1375,15 @@
         <v>11</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>5</v>
@@ -1360,10 +1396,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1384,7 +1420,7 @@
         <v>47</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1405,12 +1441,12 @@
         <v>49</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>2</v>
@@ -1420,10 +1456,10 @@
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>48</v>
@@ -1431,7 +1467,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>3</v>
@@ -1444,304 +1480,328 @@
         <v>11</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <f aca="false">SUM(B24:B29)</f>
+      <c r="B33" s="5" t="n">
+        <f aca="false">SUM(B24:B32)</f>
+        <v>29</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="D33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <f aca="false">Assumptions!$B$1*Assumptions!$B$2*D33</f>
+        <v>30</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <f aca="false">B33/F33</f>
+        <v>0.966666666666667</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="4" t="s">
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B38" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="B41" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
+      <c r="G41" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="5" t="n">
-        <f aca="false">SUM(B35:B39)</f>
-        <v>17</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="5" t="n">
+        <f aca="false">SUM(B38:B42)</f>
+        <v>20</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <f aca="false">Assumptions!$B$1*Assumptions!$B$2*D43</f>
+        <v>20</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <f aca="false">B43/F43</f>
         <v>1</v>
       </c>
-      <c r="C42" s="1" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="4" t="s">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>76</v>
-      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B48" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>14</v>
@@ -1751,18 +1811,18 @@
         <v>11</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G48" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="B49" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>14</v>
@@ -1772,279 +1832,188 @@
         <v>11</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
+      <c r="G52" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="5" t="n">
-        <f aca="false">SUM(B45:B50)</f>
-        <v>19</v>
-      </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="B56" s="5" t="n">
+        <f aca="false">SUM(B48:B55)</f>
+        <v>20</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <f aca="false">Assumptions!$B$1*Assumptions!$B$2*D56</f>
+        <v>20</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <f aca="false">B56/F56</f>
         <v>1</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <f aca="false">SUM(B56:B62)</f>
-        <v>21</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A58:G58"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2071,233 +2040,278 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>166</v>
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
